--- a/quizzes/peinture-15e-niveau2.xlsx
+++ b/quizzes/peinture-15e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A87B327-B974-4A8C-9FB0-32C32834F30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B20B95F-AC22-463C-BC39-B11A48E87145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="276">
   <si>
     <t>Image</t>
   </si>
@@ -797,12 +797,6 @@
   </si>
   <si>
     <t>« Pala di Spedaletto ». Vierge à l’Enfant </t>
-  </si>
-  <si>
-    <t>Leonard de Vinci</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b0/Annunciation_%28Leonardo%29_%28cropped%29.jpg/1280px-Annunciation_%28Leonardo%29_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>Annonciation</t>
@@ -860,7 +854,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -870,6 +864,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -936,20 +936,22 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1264,1188 +1266,1185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C8" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1463</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1486</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E19" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="E27" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1463</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="E33" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="8">
+        <v>1486</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1485</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1486</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="E39" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="6">
-        <v>1486</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="6">
-        <v>1485</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C41" s="4">
-        <v>1472</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
+      <c r="E42" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
+        <v>255</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
+      <c r="A44" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
+      <c r="A45" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
+      <c r="A46" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
+      <c r="A47" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
+      <c r="A48" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
+      <c r="A49" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
+        <v>205</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1480</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1480</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
+      <c r="A51" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+      <c r="A53" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+      <c r="A54" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
+      <c r="A56" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
+      <c r="A57" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" s="8">
+        <v>1462</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C59" s="8">
+        <v>1468</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D61" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E61" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1462</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1468</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E61">
-    <sortCondition ref="B3:B61"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E60">
+    <sortCondition ref="B3:B60"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A27" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A55" r:id="rId2" xr:uid="{DBAF7056-AD1D-4A59-A518-8DE3082EED2C}"/>
-    <hyperlink ref="A43" r:id="rId3" xr:uid="{F8BD980F-40FF-460B-A92F-B27B0752CB22}"/>
+    <hyperlink ref="A54" r:id="rId2" xr:uid="{DBAF7056-AD1D-4A59-A518-8DE3082EED2C}"/>
+    <hyperlink ref="A42" r:id="rId3" xr:uid="{F8BD980F-40FF-460B-A92F-B27B0752CB22}"/>
     <hyperlink ref="A24" r:id="rId4" xr:uid="{C8DC4018-C3DE-453A-99C2-DF808A38EEFD}"/>
-    <hyperlink ref="A50" r:id="rId5" xr:uid="{A02CCD98-CFBB-4728-8400-CE2D30A71EB6}"/>
+    <hyperlink ref="A49" r:id="rId5" xr:uid="{A02CCD98-CFBB-4728-8400-CE2D30A71EB6}"/>
     <hyperlink ref="A18" r:id="rId6" xr:uid="{ABFB350B-10CB-4CEB-99B9-0E2824CA6C0B}"/>
     <hyperlink ref="A30" r:id="rId7" xr:uid="{37AA0329-0DBC-4F91-924B-07381F64783D}"/>
-    <hyperlink ref="A48" r:id="rId8" xr:uid="{3A3EC160-45A6-4E05-B962-A7EA2C7F2D92}"/>
+    <hyperlink ref="A47" r:id="rId8" xr:uid="{3A3EC160-45A6-4E05-B962-A7EA2C7F2D92}"/>
     <hyperlink ref="A7" r:id="rId9" xr:uid="{4DBFE0AA-443E-4A2F-806C-D5C09A2E03C1}"/>
     <hyperlink ref="A33" r:id="rId10" xr:uid="{231B8196-4F15-413B-BB42-F7C508B188A1}"/>
-    <hyperlink ref="A54" r:id="rId11" xr:uid="{33698AA6-EB0F-4335-AC83-127C594AFBE8}"/>
+    <hyperlink ref="A53" r:id="rId11" xr:uid="{33698AA6-EB0F-4335-AC83-127C594AFBE8}"/>
     <hyperlink ref="A31" r:id="rId12" xr:uid="{C3321C2F-7351-43CA-8519-BD42CA1F5F7E}"/>
     <hyperlink ref="A32" r:id="rId13" xr:uid="{16E3254C-FB97-4549-A55F-0908CE01B400}"/>
     <hyperlink ref="A39" r:id="rId14" xr:uid="{78C5B9F9-14A4-4B12-A003-15FA323B2A84}"/>
-    <hyperlink ref="A49" r:id="rId15" xr:uid="{73AB1BB2-3BE0-4B37-8DBC-7F788C3410AD}"/>
-    <hyperlink ref="A42" r:id="rId16" xr:uid="{E5AE7BD9-14E6-428D-8DF4-829E0B668840}"/>
-    <hyperlink ref="A52" r:id="rId17" xr:uid="{64FE895A-A53C-4442-92EE-D17AA7955FF3}"/>
+    <hyperlink ref="A48" r:id="rId15" xr:uid="{73AB1BB2-3BE0-4B37-8DBC-7F788C3410AD}"/>
+    <hyperlink ref="A41" r:id="rId16" xr:uid="{E5AE7BD9-14E6-428D-8DF4-829E0B668840}"/>
+    <hyperlink ref="A51" r:id="rId17" xr:uid="{64FE895A-A53C-4442-92EE-D17AA7955FF3}"/>
     <hyperlink ref="A6" r:id="rId18" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/Mantegna_-_Ducal_Palace%2C_View_of_the_west_and_north_walls%2C_0sposi2.jpg/1280px-Mantegna_-_Ducal_Palace%2C_View_of_the_west_and_north_walls%2C_0sposi2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{41B0C177-EE1F-492B-B72C-50185DD44D11}"/>
     <hyperlink ref="A17" r:id="rId19" xr:uid="{AA38A7DD-57A5-4F1D-8072-B43EDC12FBB4}"/>
     <hyperlink ref="A13" r:id="rId20" xr:uid="{D4B934BB-C38A-47C8-9C4F-E66167B227C7}"/>
     <hyperlink ref="A23" r:id="rId21" xr:uid="{BC6C1BCE-CDA9-4976-A288-1D63163D0A85}"/>
-    <hyperlink ref="A61" r:id="rId22" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Accademia_-_Sogno_di_sant%27Orsola_-_Vittore_Carpaccio.jpg/1280px-Accademia_-_Sogno_di_sant%27Orsola_-_Vittore_Carpaccio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B4204C77-93D1-4040-8329-E34098FB4CD7}"/>
+    <hyperlink ref="A60" r:id="rId22" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Accademia_-_Sogno_di_sant%27Orsola_-_Vittore_Carpaccio.jpg/1280px-Accademia_-_Sogno_di_sant%27Orsola_-_Vittore_Carpaccio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B4204C77-93D1-4040-8329-E34098FB4CD7}"/>
     <hyperlink ref="A14" r:id="rId23" xr:uid="{762FE3BF-A6F7-448E-8D74-AC466DE5EE6D}"/>
     <hyperlink ref="A5" r:id="rId24" xr:uid="{780A11B8-88D0-4D60-ADF0-54EA927D5275}"/>
     <hyperlink ref="A19" r:id="rId25" xr:uid="{E2E02E8F-D480-48D0-9DE8-1EC15C666772}"/>
     <hyperlink ref="A40" r:id="rId26" xr:uid="{D4E5ACB9-83B5-4507-BDD4-81713CADACF7}"/>
-    <hyperlink ref="A58" r:id="rId27" xr:uid="{B8379FFA-4983-4DAA-92FB-EA1DA2D19777}"/>
+    <hyperlink ref="A57" r:id="rId27" xr:uid="{B8379FFA-4983-4DAA-92FB-EA1DA2D19777}"/>
     <hyperlink ref="A16" r:id="rId28" xr:uid="{1C2A9428-ABE1-447E-AA56-72E6A79022DA}"/>
-    <hyperlink ref="A45" r:id="rId29" xr:uid="{15092FA0-B176-422D-9716-BB74A76DAE76}"/>
+    <hyperlink ref="A44" r:id="rId29" xr:uid="{15092FA0-B176-422D-9716-BB74A76DAE76}"/>
     <hyperlink ref="A25" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/42/Madonna_and_Child_with_two_Angels_%28by_Filippo_Lippi%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg/960px-Madonna_and_Child_with_two_Angels_%28by_Filippo_Lippi%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{78EA8A3D-0359-4076-8A56-479BE40FE011}"/>
-    <hyperlink ref="A51" r:id="rId31" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1d/Piero_di_Cosimo_-_Portrait_de_femme_dit_de_Simonetta_Vespucci_-_Google_Art_Project.jpg/960px-Piero_di_Cosimo_-_Portrait_de_femme_dit_de_Simonetta_Vespucci_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{010F3F2C-5C3C-4C62-A5D4-7C44075439AB}"/>
+    <hyperlink ref="A50" r:id="rId31" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1d/Piero_di_Cosimo_-_Portrait_de_femme_dit_de_Simonetta_Vespucci_-_Google_Art_Project.jpg/960px-Piero_di_Cosimo_-_Portrait_de_femme_dit_de_Simonetta_Vespucci_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{010F3F2C-5C3C-4C62-A5D4-7C44075439AB}"/>
     <hyperlink ref="A28" r:id="rId32" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3c/Gentile_da_Fabriano_-_Adorazione_dei_Magi_-_Google_Art_Project.jpg/1920px-Gentile_da_Fabriano_-_Adorazione_dei_Magi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{58AB5877-A255-4CAB-99A9-0568EFC549A5}"/>
     <hyperlink ref="A4" r:id="rId33" xr:uid="{928EAD2D-33F4-4E5C-8826-7EB2E22E31CA}"/>
-    <hyperlink ref="A56" r:id="rId34" xr:uid="{8112CC4C-1DF6-4AC6-8007-552EBF7459CE}"/>
+    <hyperlink ref="A55" r:id="rId34" xr:uid="{8112CC4C-1DF6-4AC6-8007-552EBF7459CE}"/>
     <hyperlink ref="A15" r:id="rId35" xr:uid="{7A90DD24-C418-47E6-8327-09E1ED3A6727}"/>
     <hyperlink ref="A26" r:id="rId36" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/Francesco_del_Cossa%2C_May%2C_fresco%2C_Palazzo_Schifanoia%2C_1470.jpg/960px-Francesco_del_Cossa%2C_May%2C_fresco%2C_Palazzo_Schifanoia%2C_1470.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9EACD076-AF5B-4057-8248-E70A3FF093B5}"/>
     <hyperlink ref="A21" r:id="rId37" xr:uid="{A9898024-4EEF-485A-9799-2EDB9C581F2C}"/>
-    <hyperlink ref="A53" r:id="rId38" xr:uid="{7B438D4C-C997-40B5-9E34-EA335FCE42A8}"/>
+    <hyperlink ref="A52" r:id="rId38" xr:uid="{7B438D4C-C997-40B5-9E34-EA335FCE42A8}"/>
     <hyperlink ref="A37" r:id="rId39" xr:uid="{66E9A9E1-7ED2-42F4-A7DC-0B099B044DDF}"/>
     <hyperlink ref="A20" r:id="rId40" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/fb/Enguerrand_Quarton%2C_La_Piet%C3%A0_de_Villeneuve-l%C3%A8s-Avignon_%28c._1455%29.jpg/1280px-Enguerrand_Quarton%2C_La_Piet%C3%A0_de_Villeneuve-l%C3%A8s-Avignon_%28c._1455%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C004A7B-2548-45BE-B438-57F9F321D28B}"/>
-    <hyperlink ref="A46" r:id="rId41" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/St._Wolfgang_%28St._Wolfgang%29%2C_Hauptaltar%2C_2024-10-17.jpg/1280px-St._Wolfgang_%28St._Wolfgang%29%2C_Hauptaltar%2C_2024-10-17.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96CAE3F3-75E5-4A63-B6CA-FD275A65CBF9}"/>
+    <hyperlink ref="A45" r:id="rId41" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/St._Wolfgang_%28St._Wolfgang%29%2C_Hauptaltar%2C_2024-10-17.jpg/1280px-St._Wolfgang_%28St._Wolfgang%29%2C_Hauptaltar%2C_2024-10-17.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96CAE3F3-75E5-4A63-B6CA-FD275A65CBF9}"/>
     <hyperlink ref="A11" r:id="rId42" xr:uid="{13AA895B-0477-4F96-85E2-087BF4693241}"/>
     <hyperlink ref="A35" r:id="rId43" xr:uid="{9620B3E0-3F61-40F1-A93D-7F90474E6269}"/>
     <hyperlink ref="A36" r:id="rId44" xr:uid="{677A954D-FC2D-426D-82B9-6B9B8E01051E}"/>
     <hyperlink ref="A38" r:id="rId45" xr:uid="{32E6E2E8-28C9-4363-8173-4BD9AE610608}"/>
-    <hyperlink ref="A57" r:id="rId46" xr:uid="{9FCF6FE6-E77F-4734-B35A-34ABEDFCFF20}"/>
+    <hyperlink ref="A56" r:id="rId46" xr:uid="{9FCF6FE6-E77F-4734-B35A-34ABEDFCFF20}"/>
     <hyperlink ref="A29" r:id="rId47" xr:uid="{E214C092-B60D-4861-95CA-9966F5829BEE}"/>
-    <hyperlink ref="A47" r:id="rId48" xr:uid="{95FA0C33-DAC6-4E24-B3EF-64A4A62CBBB8}"/>
+    <hyperlink ref="A46" r:id="rId48" xr:uid="{95FA0C33-DAC6-4E24-B3EF-64A4A62CBBB8}"/>
     <hyperlink ref="A34" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/ab/Barcelona_Cathedral_Interior_-_Chapel_of_Saint_Sebastian_and_Saint_Thecla_1486-1498_Jaume_Huguet.jpg/1920px-Barcelona_Cathedral_Interior_-_Chapel_of_Saint_Sebastian_and_Saint_Thecla_1486-1498_Jaume_Huguet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{60B499F2-368E-46EC-82CF-45B66C1FC61D}"/>
     <hyperlink ref="A22" r:id="rId50" xr:uid="{9338C023-A232-46AC-9CC1-2D83546CB399}"/>
     <hyperlink ref="A9" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/Antonio_vivarini%2C_polittico_di_sant%27antonio_abate%2C_1464.JPG/960px-Antonio_vivarini%2C_polittico_di_sant%27antonio_abate%2C_1464.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4EB4650F-7E8C-4726-8375-965C7D1F8B74}"/>
     <hyperlink ref="A12" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/31/0_Venise%2C_Pala_di_San_Marco._-_Basilica_Santa_Maria_Gloriosa_dei_Frari.JPG/960px-0_Venise%2C_Pala_di_San_Marco._-_Basilica_Santa_Maria_Gloriosa_dei_Frari.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8A60566-B05F-4790-939D-E1D4C28A481A}"/>
-    <hyperlink ref="A44" r:id="rId53" xr:uid="{734C6D48-AB01-4410-885E-F20D9E69BBBB}"/>
+    <hyperlink ref="A43" r:id="rId53" xr:uid="{734C6D48-AB01-4410-885E-F20D9E69BBBB}"/>
     <hyperlink ref="A3" r:id="rId54" xr:uid="{32845A08-6B7B-49B6-8AF2-780B753D81D0}"/>
-    <hyperlink ref="A59" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/e/e4/Lorenzo_di_Pietro_known_as_%22Vecchietta%22_-_%22Pala_di_Spedaletto%22._Madonna_with_Child_and_Saints_Biagio%2C_John_the_Baptist%2C_Nicola_and_Floriano%3B_A..._-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{49BA43A1-4A0E-4E23-A0B2-C23E7D1B4A27}"/>
-    <hyperlink ref="A41" r:id="rId56" xr:uid="{A330C482-32AE-40BF-A83F-5EDD1AB62587}"/>
-    <hyperlink ref="A2" r:id="rId57" xr:uid="{930A8A29-E1B8-4F32-BCE9-03CA9C48A38E}"/>
-    <hyperlink ref="A8" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bb/London_National_Gallery_Pollaiuolo_Saint_Sebastian.jpg/960px-London_National_Gallery_Pollaiuolo_Saint_Sebastian.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BE65EC48-2BC9-43CF-9E1C-48F30BBA5FAE}"/>
-    <hyperlink ref="A60" r:id="rId59" xr:uid="{77BCFA93-4284-4DE6-8481-D7BEB8ED3C03}"/>
-    <hyperlink ref="A10" r:id="rId60" xr:uid="{150646AE-A459-423B-80CA-13DEB67BD242}"/>
+    <hyperlink ref="A58" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/e/e4/Lorenzo_di_Pietro_known_as_%22Vecchietta%22_-_%22Pala_di_Spedaletto%22._Madonna_with_Child_and_Saints_Biagio%2C_John_the_Baptist%2C_Nicola_and_Floriano%3B_A..._-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{49BA43A1-4A0E-4E23-A0B2-C23E7D1B4A27}"/>
+    <hyperlink ref="A2" r:id="rId56" xr:uid="{930A8A29-E1B8-4F32-BCE9-03CA9C48A38E}"/>
+    <hyperlink ref="A8" r:id="rId57" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bb/London_National_Gallery_Pollaiuolo_Saint_Sebastian.jpg/960px-London_National_Gallery_Pollaiuolo_Saint_Sebastian.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BE65EC48-2BC9-43CF-9E1C-48F30BBA5FAE}"/>
+    <hyperlink ref="A59" r:id="rId58" xr:uid="{77BCFA93-4284-4DE6-8481-D7BEB8ED3C03}"/>
+    <hyperlink ref="A10" r:id="rId59" xr:uid="{150646AE-A459-423B-80CA-13DEB67BD242}"/>
+    <hyperlink ref="A61" r:id="rId60" xr:uid="{88932CBA-ED68-492A-884E-6A38F3E095DC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-15e-niveau2.xlsx
+++ b/quizzes/peinture-15e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F71E37B-7782-4030-B553-276054E162DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDFA80DE-8A2C-42AA-9B2D-056EE26B916D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="396">
   <si>
     <t>Image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/51/Alesso_baldovinetti%2C_nativit%C3%A0.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>dimensions non standardisées</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5b/Alvise_vivarini%2C_retablo_della_pentecoste%2C_1478.JPG/960px-Alvise_vivarini%2C_retablo_della_pentecoste%2C_1478.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -232,6 +238,9 @@
     <t>98 × 217 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/3/3b/Santo_Domingo_de_Silos_entronizado_como_obispo%2C_por_Bartolom%C3%A9_Bermejo.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -253,6 +262,9 @@
     <t>242 × 130 cm</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/31/0_Venise%2C_Pala_di_San_Marco._-_Basilica_Santa_Maria_Gloriosa_dei_Frari.JPG/960px-0_Venise%2C_Pala_di_San_Marco._-_Basilica_Santa_Maria_Gloriosa_dei_Frari.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -358,6 +370,9 @@
     <t>vers 1415-1475</t>
   </si>
   <si>
+    <t>flamande (Belgique)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/91/Birth_of_St_Mary_in_Santa_Maria_Novella_in_Firenze_by_Domenico_Ghirlandaio.jpg/1280px-Birth_of_St_Mary_in_Santa_Maria_Novella_in_Firenze_by_Domenico_Ghirlandaio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -586,6 +601,9 @@
     <t>vers 1460-1523</t>
   </si>
   <si>
+    <t>hollandaise (Pays-Bas)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Giovanni_Bellini_-_Trasfigurazione_di_Cristo.jpg/1280px-Giovanni_Bellini_-_Trasfigurazione_di_Cristo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -682,6 +700,9 @@
     <t>vers 1412-1492</t>
   </si>
   <si>
+    <t>catalane (Espagne)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Jean_Bourdichon_-_Adoration_of_the_Magi_-_WGA02939.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -802,6 +823,9 @@
     <t>132 × 154 cm</t>
   </si>
   <si>
+    <t>suisse</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/35/Signorelli_Resurrection.jpg/1280px-Signorelli_Resurrection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -898,6 +922,9 @@
     <t>Bois polychrome doré</t>
   </si>
   <si>
+    <t>autrichienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c7/Lagos40_kopie.jpg/3840px-Lagos40_kopie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -919,6 +946,9 @@
     <t>dimensions architecturales (polyptyque)</t>
   </si>
   <si>
+    <t>portugaise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/Uccello_Battle_of_San_Romano_Uffizi.jpg/1280px-Uccello_Battle_of_San_Romano_Uffizi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1124,6 +1154,9 @@
   </si>
   <si>
     <t>51 × 40 cm</t>
+  </si>
+  <si>
+    <t>allemande</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/e/e4/Lorenzo_di_Pietro_known_as_%22Vecchietta%22_-_%22Pala_di_Spedaletto%22._Madonna_with_Child_and_Saints_Biagio%2C_John_the_Baptist%2C_Nicola_and_Floriano%3B_A..._-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -1607,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="107.140625" style="8" customWidth="1"/>
@@ -1620,7 +1653,7 @@
     <col min="8" max="8" width="37.5703125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="12" customFormat="1">
+    <row r="1" spans="1:9" s="12" customFormat="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1645,1565 +1678,1748 @@
       <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="H8" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10" s="5">
         <v>1463</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>71</v>
+      </c>
+      <c r="I10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>79</v>
+      </c>
+      <c r="I11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C14" s="5">
         <v>1486</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>98</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="I20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="I31" t="s">
         <v>116</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F30" s="8" t="s">
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="I32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I33" t="s">
         <v>193</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C34" s="5">
         <v>1486</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>234</v>
+      </c>
+      <c r="I35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F36" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="G36" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>226</v>
-      </c>
       <c r="H36" s="8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>234</v>
+      </c>
+      <c r="I36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>247</v>
+      </c>
+      <c r="I37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C38" s="5">
         <v>1485</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>253</v>
+      </c>
+      <c r="I38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="4" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>259</v>
+      </c>
+      <c r="I39" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="4" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>266</v>
+      </c>
+      <c r="I40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="4" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>279</v>
+      </c>
+      <c r="I42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>292</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I45" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>307</v>
+      </c>
+      <c r="I46" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>314</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>321</v>
+      </c>
+      <c r="I48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="4" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>328</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C50" s="5">
         <v>1480</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>334</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="4" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>339</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="4" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>351</v>
+      </c>
+      <c r="I53" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="4" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>358</v>
+      </c>
+      <c r="I54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>365</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="I56" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="4" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>377</v>
+      </c>
+      <c r="I57" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C58" s="5">
         <v>1462</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C59" s="5">
         <v>1468</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="I60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F61" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="G61" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="G59" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="2" t="s">
+      <c r="I61" t="s">
         <v>378</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="8" t="s">
-        <v>367</v>
       </c>
     </row>
   </sheetData>
